--- a/data/GPS/Metricas_GPS36.xlsx
+++ b/data/GPS/Metricas_GPS36.xlsx
@@ -12,35 +12,35 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
   <si>
     <t>Fecha</t>
   </si>
   <si>
-    <t>eJy9lltv2jAUx7+KladNQiEJK2PTNIkN9WUto53arruoMrZDXHyJYru0IL77bMO6kAErmZqn5Jwcn/P7H9+yCDDURAVvwSLQ0j+cw74ESZR04yiOghYI7iBzLuZidbC0nrSQ/KnhLj6/0yiduELfF2vjhmIXxY3BcE67vZkbiiRbB9m3dcRczKj7lkOdOduXtLZ+yEnZFpB7+5igDDqHEVQ7hyMuJ2SR1Wq/U3Uz8fQpZIpYR0GwQT6HltqXgBNM0tWwuHv0pmN9RBhuPR7zZwkrlyokOSqT2eFlDk5FmXNgCoioFFW8Y3h2Wdbr40tZcwYfSFHONJR8XJB9kr+dJx+DTViqXe29eUc2Cq2jdmXG1Nxubea4MCojj236795iqvb0dso3WkuVhgJRCGwxuxorzJ+yq94Gsy7McyDPBQlf1QR/D+IemPJ2VoU/6ZqsKfhuTXhLnxy1ErBVwGd+cdqUgNc1Bbj+J71Wb7uCMwnvm5sCJPQeBRvnwA8TRWMIvuQFFVqBF+/+zMLLv9aR+NBvQgREyOlIaujoI8LI6pC0QBX++PxrI5sYk9r8A6LgPgkXQ3V92NnJVwuvxhyEv4fuuJvaqq3KGvooBKfwnnJYpUYjgg+kXl18taipOIR6QHZi52mn00izVY7/0Wy3Hzcu2ksPXSUeJNfDZ79a6a0KmcRPXNkj/48ATiTEwdKlQYwSoVelhGHMOx/3AZmBK1lMx1JOg+UvE5oQVA==</t>
+    <t>eJy9lltv2jAUx7+KladNQiGElbFpmsSG+rKW0U5t111UGdshLr5EsV1aEN99tsO6kAErmZqn5Jwcn/P7H9+yDDDURAVvwTLQ0j+cw74EcRT3OlGnG7RAcAeZczEXq4OV9SS55E8Nd/HZnUbJ1BX6vlwbNxS7KG4Mhgva68/dUCTZOsi+rSMWYk7dtwzq1Nm+pLX1Q0bKtoDc28cEpdA5jKDaORxxOSGLrFb7naqbqadPIFPEOnKCDfI5tNS+BJxikhTDOr2jN13rI8Jw6/GYP0tYmVQhyVCZzA4vc3AqypxDk0NEpajiHcOzy7JeH1/KmjH4QPJyppHkk5zsk/ztPP4YbMJS7WrvzTu2UWgdtSszpuZ2azMnuVEpeWzTf/cWU7WntzO+0VqqNBSIQmCL2dVYYf6UXvU3mHVungN5IUj4qib4e9Dpgxlvp1X4k55Jm4Lv1YS39PFRKwZbBXzmF6dNCXhdU4Drf9xv9bcrOJPwvrkpQELvUbBxDvwwUTSB4EuWU6EVePHuzyy8/GsdiQ+DJkRAhJyOuIaOASKMFIekBarwd86/NrKJManNPyQK7pNwMVLXh52dvFh4NeYg/D10x93UVm1V1jBAITiF95TDKjUaE3wgdXHx1aKm4hDqIdmJnSXdbiPNVhn+R7Pdfty4aC89dJV4GF+Pnv1qpbcqZBI/cWWP/T8COJEQByuXBjFKhC5KCcOYdz7uAzIHVzKfTaScBatfUM8QWg==</t>
   </si>
   <si>
     <t>Duracion</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>Nombre</t>
   </si>
   <si>
+    <t>DO NOT EDIT THIS SHEET</t>
+  </si>
+  <si>
     <t>Posicion</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Distancia total</t>
   </si>
   <si>
     <t>Distancia &gt; 18 km/h</t>
   </si>
   <si>
-    <t>DO NOT EDIT THIS SHEET</t>
-  </si>
-  <si>
     <t>Distancia  &gt; 25,2  km/h</t>
   </si>
   <si>
@@ -68,64 +68,49 @@
     <t>Player Load</t>
   </si>
   <si>
-    <t xml:space="preserve">Presley_Osarenkhoe </t>
+    <t xml:space="preserve">Rodri_Sanchez_Ramos </t>
+  </si>
+  <si>
+    <t>Mediapunta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petko_Avramov </t>
+  </si>
+  <si>
+    <t>Defensa Central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guillermo_Garcia_Lapena </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jorge_vicaria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noah_Ojo_Barranco </t>
+  </si>
+  <si>
+    <t>Defensa Lateral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alberto_Benedicto_Carpintero </t>
+  </si>
+  <si>
+    <t>Mediocentro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gonzalo_Kvisz </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luis_Moliner </t>
+  </si>
+  <si>
+    <t>Extremo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex_Palacios </t>
   </si>
   <si>
     <t>Delantero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alejandro_Dominguez_Gonzalez </t>
-  </si>
-  <si>
-    <t>Defensa Lateral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex_Balbure </t>
-  </si>
-  <si>
-    <t>Defensa Central</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rodri_Sanchez_Ramos </t>
-  </si>
-  <si>
-    <t>Mediapunta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petko_Avramov </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carlos_De_La_Fe_Simon </t>
-  </si>
-  <si>
-    <t>Mediocentro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guillermo_Garcia_Lapena </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex_Palacios </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noah_Ojo_Barranco </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samuel_Chaparro_Garcia </t>
-  </si>
-  <si>
-    <t>Extremo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alberto_Benedicto_Carpintero </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gonzalo_Kvisz </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luis_Moliner </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marco_Sanchez_Arias </t>
   </si>
   <si>
     <t xml:space="preserve">Ruben_Perez_Curto </t>
@@ -416,10 +401,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -445,16 +430,16 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
@@ -486,10 +471,10 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46305.0</v>
+        <v>46308.0</v>
       </c>
       <c r="B2" s="1">
-        <v>161.75</v>
+        <v>84.583</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>18</v>
@@ -498,45 +483,45 @@
         <v>19</v>
       </c>
       <c r="E2" s="1">
-        <v>7.769</v>
+        <v>6.723</v>
       </c>
       <c r="F2" s="1">
-        <v>0.645</v>
+        <v>0.391</v>
       </c>
       <c r="G2" s="1">
-        <v>0.042</v>
+        <v>0.003</v>
       </c>
       <c r="H2" s="1">
-        <v>0.003</v>
+        <v>0.0</v>
       </c>
       <c r="I2" s="1">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="J2" s="1">
-        <v>41.0</v>
+        <v>34.0</v>
       </c>
       <c r="K2" s="1">
-        <v>30.0</v>
+        <v>45.0</v>
       </c>
       <c r="L2" s="1">
-        <v>4.515</v>
+        <v>5.018</v>
       </c>
       <c r="M2" s="1">
-        <v>-5.0</v>
+        <v>-5.197</v>
       </c>
       <c r="N2" s="1">
-        <v>29.142</v>
+        <v>26.165</v>
       </c>
       <c r="O2" s="1">
-        <v>1400.846</v>
+        <v>1164.616</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <v>46305.0</v>
+        <v>46308.0</v>
       </c>
       <c r="B3" s="1">
-        <v>124.567</v>
+        <v>83.533</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>20</v>
@@ -545,695 +530,460 @@
         <v>21</v>
       </c>
       <c r="E3" s="1">
-        <v>10.049</v>
+        <v>6.261</v>
       </c>
       <c r="F3" s="1">
-        <v>0.679</v>
+        <v>0.11</v>
       </c>
       <c r="G3" s="1">
-        <v>0.087</v>
+        <v>0.002</v>
       </c>
       <c r="H3" s="1">
-        <v>0.004</v>
+        <v>0.0</v>
       </c>
       <c r="I3" s="1">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="J3" s="1">
-        <v>41.0</v>
+        <v>54.0</v>
       </c>
       <c r="K3" s="1">
-        <v>53.0</v>
+        <v>37.0</v>
       </c>
       <c r="L3" s="1">
-        <v>4.576</v>
+        <v>5.296</v>
       </c>
       <c r="M3" s="1">
-        <v>-5.751</v>
+        <v>-5.716</v>
       </c>
       <c r="N3" s="1">
-        <v>29.426</v>
+        <v>26.464</v>
       </c>
       <c r="O3" s="1">
-        <v>1987.507</v>
+        <v>931.156</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>46305.0</v>
+        <v>46308.0</v>
       </c>
       <c r="B4" s="1">
-        <v>131.2</v>
+        <v>71.283</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1">
-        <v>6.769</v>
+        <v>3.947</v>
       </c>
       <c r="F4" s="1">
-        <v>0.198</v>
+        <v>0.106</v>
       </c>
       <c r="G4" s="1">
-        <v>0.025</v>
+        <v>0.001</v>
       </c>
       <c r="H4" s="1">
-        <v>0.002</v>
+        <v>0.0</v>
       </c>
       <c r="I4" s="1">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="J4" s="1">
-        <v>31.0</v>
+        <v>37.0</v>
       </c>
       <c r="K4" s="1">
-        <v>21.0</v>
+        <v>12.0</v>
       </c>
       <c r="L4" s="1">
-        <v>4.578</v>
+        <v>5.187</v>
       </c>
       <c r="M4" s="1">
-        <v>-7.077</v>
+        <v>-5.302</v>
       </c>
       <c r="N4" s="1">
-        <v>28.85</v>
+        <v>25.333</v>
       </c>
       <c r="O4" s="1">
-        <v>1266.98</v>
+        <v>631.609</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <v>46305.0</v>
+        <v>46308.0</v>
       </c>
       <c r="B5" s="1">
-        <v>130.15</v>
+        <v>84.733</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1">
-        <v>10.138</v>
+        <v>5.217</v>
       </c>
       <c r="F5" s="1">
-        <v>0.729</v>
+        <v>0.09</v>
       </c>
       <c r="G5" s="1">
-        <v>0.016</v>
+        <v>0.0</v>
       </c>
       <c r="H5" s="1">
         <v>0.0</v>
       </c>
       <c r="I5" s="1">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J5" s="1">
-        <v>33.0</v>
+        <v>44.0</v>
       </c>
       <c r="K5" s="1">
-        <v>49.0</v>
+        <v>36.0</v>
       </c>
       <c r="L5" s="1">
-        <v>4.204</v>
+        <v>4.589</v>
       </c>
       <c r="M5" s="1">
-        <v>-5.525</v>
+        <v>-4.963</v>
       </c>
       <c r="N5" s="1">
-        <v>26.514</v>
+        <v>24.57</v>
       </c>
       <c r="O5" s="1">
-        <v>1887.872</v>
+        <v>1055.866</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <v>46305.0</v>
+        <v>46308.0</v>
       </c>
       <c r="B6" s="1">
-        <v>149.9</v>
+        <v>87.55</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E6" s="1">
-        <v>7.688</v>
+        <v>6.302</v>
       </c>
       <c r="F6" s="1">
-        <v>0.573</v>
+        <v>0.38</v>
       </c>
       <c r="G6" s="1">
-        <v>0.051</v>
+        <v>0.025</v>
       </c>
       <c r="H6" s="1">
-        <v>0.0</v>
+        <v>0.002</v>
       </c>
       <c r="I6" s="1">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
       <c r="J6" s="1">
-        <v>40.0</v>
+        <v>53.0</v>
       </c>
       <c r="K6" s="1">
-        <v>36.0</v>
+        <v>43.0</v>
       </c>
       <c r="L6" s="1">
-        <v>5.101</v>
+        <v>4.759</v>
       </c>
       <c r="M6" s="1">
-        <v>-6.392</v>
+        <v>-5.256</v>
       </c>
       <c r="N6" s="1">
-        <v>28.771</v>
+        <v>29.405</v>
       </c>
       <c r="O6" s="1">
-        <v>1174.873</v>
+        <v>1329.741</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <v>46305.0</v>
+        <v>46308.0</v>
       </c>
       <c r="B7" s="1">
-        <v>168.65</v>
+        <v>85.117</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="E7" s="1">
-        <v>6.955</v>
+        <v>5.698</v>
       </c>
       <c r="F7" s="1">
-        <v>0.865</v>
+        <v>0.201</v>
       </c>
       <c r="G7" s="1">
-        <v>0.05</v>
+        <v>0.004</v>
       </c>
       <c r="H7" s="1">
-        <v>0.019</v>
+        <v>0.0</v>
       </c>
       <c r="I7" s="1">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="J7" s="1">
-        <v>49.0</v>
+        <v>46.0</v>
       </c>
       <c r="K7" s="1">
-        <v>43.0</v>
+        <v>47.0</v>
       </c>
       <c r="L7" s="1">
-        <v>4.634</v>
+        <v>5.317</v>
       </c>
       <c r="M7" s="1">
-        <v>-5.486</v>
+        <v>-5.028</v>
       </c>
       <c r="N7" s="1">
-        <v>31.37</v>
+        <v>27.792</v>
       </c>
       <c r="O7" s="1">
-        <v>1186.261</v>
+        <v>1423.187</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <v>46305.0</v>
+        <v>46308.0</v>
       </c>
       <c r="B8" s="1">
-        <v>153.683</v>
+        <v>86.95</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1">
-        <v>12.419</v>
+        <v>5.415</v>
       </c>
       <c r="F8" s="1">
-        <v>0.822</v>
+        <v>0.193</v>
       </c>
       <c r="G8" s="1">
-        <v>0.053</v>
+        <v>0.005</v>
       </c>
       <c r="H8" s="1">
-        <v>0.014</v>
+        <v>0.0</v>
       </c>
       <c r="I8" s="1">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="J8" s="1">
-        <v>76.0</v>
+        <v>31.0</v>
       </c>
       <c r="K8" s="1">
-        <v>79.0</v>
+        <v>38.0</v>
       </c>
       <c r="L8" s="1">
-        <v>4.923</v>
+        <v>4.823</v>
       </c>
       <c r="M8" s="1">
-        <v>-6.003</v>
+        <v>-4.854</v>
       </c>
       <c r="N8" s="1">
-        <v>30.053</v>
+        <v>26.064</v>
       </c>
       <c r="O8" s="1">
-        <v>2464.198</v>
+        <v>851.016</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <v>46305.0</v>
+        <v>46308.0</v>
       </c>
       <c r="B9" s="1">
-        <v>153.9</v>
+        <v>71.45</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="E9" s="1">
-        <v>9.618</v>
+        <v>5.779</v>
       </c>
       <c r="F9" s="1">
-        <v>0.897</v>
+        <v>0.303</v>
       </c>
       <c r="G9" s="1">
-        <v>0.147</v>
+        <v>0.019</v>
       </c>
       <c r="H9" s="1">
-        <v>0.024</v>
+        <v>0.0</v>
       </c>
       <c r="I9" s="1">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="J9" s="1">
-        <v>53.0</v>
+        <v>42.0</v>
       </c>
       <c r="K9" s="1">
-        <v>61.0</v>
+        <v>39.0</v>
       </c>
       <c r="L9" s="1">
-        <v>5.635</v>
+        <v>4.758</v>
       </c>
       <c r="M9" s="1">
-        <v>-5.772</v>
+        <v>-5.619</v>
       </c>
       <c r="N9" s="1">
-        <v>32.846</v>
+        <v>28.624</v>
       </c>
       <c r="O9" s="1">
-        <v>2005.26</v>
+        <v>1363.188</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <v>46305.0</v>
+        <v>46308.0</v>
       </c>
       <c r="B10" s="1">
-        <v>144.45</v>
+        <v>83.917</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E10" s="1">
-        <v>10.037</v>
+        <v>5.39</v>
       </c>
       <c r="F10" s="1">
-        <v>0.673</v>
+        <v>0.177</v>
       </c>
       <c r="G10" s="1">
-        <v>0.093</v>
+        <v>0.006</v>
       </c>
       <c r="H10" s="1">
-        <v>0.017</v>
+        <v>0.0</v>
       </c>
       <c r="I10" s="1">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="J10" s="1">
-        <v>49.0</v>
+        <v>45.0</v>
       </c>
       <c r="K10" s="1">
-        <v>46.0</v>
+        <v>34.0</v>
       </c>
       <c r="L10" s="1">
-        <v>5.171</v>
+        <v>4.461</v>
       </c>
       <c r="M10" s="1">
-        <v>-6.245</v>
+        <v>-4.961</v>
       </c>
       <c r="N10" s="1">
-        <v>30.974</v>
+        <v>26.1</v>
       </c>
       <c r="O10" s="1">
-        <v>2016.948</v>
+        <v>1117.541</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <v>46305.0</v>
+        <v>46308.0</v>
       </c>
       <c r="B11" s="1">
-        <v>169.233</v>
+        <v>85.333</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E11" s="1">
-        <v>7.676</v>
+        <v>6.683</v>
       </c>
       <c r="F11" s="1">
-        <v>1.342</v>
+        <v>0.334</v>
       </c>
       <c r="G11" s="1">
-        <v>0.167</v>
+        <v>0.019</v>
       </c>
       <c r="H11" s="1">
-        <v>0.008</v>
+        <v>0.0</v>
       </c>
       <c r="I11" s="1">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="J11" s="1">
-        <v>63.0</v>
+        <v>52.0</v>
       </c>
       <c r="K11" s="1">
-        <v>52.0</v>
+        <v>49.0</v>
       </c>
       <c r="L11" s="1">
-        <v>5.041</v>
+        <v>5.607</v>
       </c>
       <c r="M11" s="1">
-        <v>-5.91</v>
+        <v>-4.944</v>
       </c>
       <c r="N11" s="1">
-        <v>30.136</v>
+        <v>28.328</v>
       </c>
       <c r="O11" s="1">
-        <v>1748.318</v>
+        <v>1509.656</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
-        <v>46305.0</v>
+        <v>46308.0</v>
       </c>
       <c r="B12" s="1">
-        <v>215.65</v>
+        <v>84.017</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E12" s="1">
-        <v>14.968</v>
+        <v>6.3</v>
       </c>
       <c r="F12" s="1">
-        <v>0.886</v>
+        <v>0.38</v>
       </c>
       <c r="G12" s="1">
-        <v>0.042</v>
+        <v>0.037</v>
       </c>
       <c r="H12" s="1">
         <v>0.001</v>
       </c>
       <c r="I12" s="1">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="J12" s="1">
-        <v>90.0</v>
+        <v>61.0</v>
       </c>
       <c r="K12" s="1">
-        <v>129.0</v>
+        <v>49.0</v>
       </c>
       <c r="L12" s="1">
-        <v>4.913</v>
+        <v>5.036</v>
       </c>
       <c r="M12" s="1">
-        <v>-6.667</v>
+        <v>-5.043</v>
       </c>
       <c r="N12" s="1">
-        <v>29.79</v>
+        <v>28.872</v>
       </c>
       <c r="O12" s="1">
-        <v>3216.601</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3">
-        <v>46305.0</v>
-      </c>
-      <c r="B13" s="1">
-        <v>154.217</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="1">
-        <v>11.535</v>
-      </c>
-      <c r="F13" s="1">
-        <v>0.627</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0.016</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I13" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>56.0</v>
-      </c>
-      <c r="L13" s="1">
-        <v>4.547</v>
-      </c>
-      <c r="M13" s="1">
-        <v>-6.162</v>
-      </c>
-      <c r="N13" s="1">
-        <v>28.426</v>
-      </c>
-      <c r="O13" s="1">
-        <v>2017.41</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3">
-        <v>46305.0</v>
-      </c>
-      <c r="B14" s="1">
-        <v>154.217</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="1">
-        <v>13.326</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1.409</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0.203</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0.034</v>
-      </c>
-      <c r="I14" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="J14" s="1">
-        <v>91.0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>91.0</v>
-      </c>
-      <c r="L14" s="1">
-        <v>5.004</v>
-      </c>
-      <c r="M14" s="1">
-        <v>-5.824</v>
-      </c>
-      <c r="N14" s="1">
-        <v>30.881</v>
-      </c>
-      <c r="O14" s="1">
-        <v>3378.668</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3">
-        <v>46305.0</v>
-      </c>
-      <c r="B15" s="1">
-        <v>168.567</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="1">
-        <v>5.049</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0.975</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0.185</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0.026</v>
-      </c>
-      <c r="I15" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="J15" s="1">
-        <v>59.0</v>
-      </c>
-      <c r="K15" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="L15" s="1">
-        <v>5.447</v>
-      </c>
-      <c r="M15" s="1">
-        <v>-4.795</v>
-      </c>
-      <c r="N15" s="1">
-        <v>30.283</v>
-      </c>
-      <c r="O15" s="1">
-        <v>920.223</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3">
-        <v>46305.0</v>
-      </c>
-      <c r="B16" s="1">
-        <v>152.633</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="1">
-        <v>12.955</v>
-      </c>
-      <c r="F16" s="1">
-        <v>1.437</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0.134</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="J16" s="1">
-        <v>72.0</v>
-      </c>
-      <c r="K16" s="1">
-        <v>88.0</v>
-      </c>
-      <c r="L16" s="1">
-        <v>4.726</v>
-      </c>
-      <c r="M16" s="1">
-        <v>-6.885</v>
-      </c>
-      <c r="N16" s="1">
-        <v>28.746</v>
-      </c>
-      <c r="O16" s="1">
-        <v>2862.178</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3">
-        <v>46305.0</v>
-      </c>
-      <c r="B17" s="1">
-        <v>168.9</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="1">
-        <v>6.454</v>
-      </c>
-      <c r="F17" s="1">
-        <v>0.989</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0.128</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0.019</v>
-      </c>
-      <c r="I17" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="J17" s="1">
-        <v>57.0</v>
-      </c>
-      <c r="K17" s="1">
-        <v>50.0</v>
-      </c>
-      <c r="L17" s="1">
-        <v>5.306</v>
-      </c>
-      <c r="M17" s="1">
-        <v>-4.8</v>
-      </c>
-      <c r="N17" s="1">
-        <v>30.362</v>
-      </c>
-      <c r="O17" s="1">
-        <v>1088.257</v>
+        <v>1209.547</v>
       </c>
     </row>
   </sheetData>
